--- a/ВКР, программное обеспечение/ВКР, датасет.xlsx
+++ b/ВКР, программное обеспечение/ВКР, датасет.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузки\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\PycharmProjects\Diploma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD3BEB5-52AD-48B5-811F-01B7C1F84B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED44AC7-2832-4DFC-B278-9CDBE1E65625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,25 +41,7 @@
     <t>NUM</t>
   </si>
   <si>
-    <t>NI</t>
-  </si>
-  <si>
-    <t>CR</t>
-  </si>
-  <si>
-    <t>CO</t>
-  </si>
-  <si>
     <t>W</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>AL</t>
   </si>
   <si>
     <t>C</t>
@@ -68,40 +50,10 @@
     <t>V</t>
   </si>
   <si>
-    <t>TA</t>
-  </si>
-  <si>
-    <t>NB</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>MN</t>
-  </si>
-  <si>
-    <t>FE</t>
-  </si>
-  <si>
-    <t>CE</t>
-  </si>
-  <si>
-    <t>CU</t>
-  </si>
-  <si>
-    <t>BE</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
     <t>S</t>
-  </si>
-  <si>
-    <t>LA</t>
-  </si>
-  <si>
-    <t>SN</t>
   </si>
   <si>
     <t>g</t>
@@ -126,6 +78,54 @@
   </si>
   <si>
     <t>КТР25-500</t>
+  </si>
+  <si>
+    <t>Ni</t>
+  </si>
+  <si>
+    <t>Cr</t>
+  </si>
+  <si>
+    <t>Co</t>
+  </si>
+  <si>
+    <t>Mo</t>
+  </si>
+  <si>
+    <t>Ti</t>
+  </si>
+  <si>
+    <t>Al</t>
+  </si>
+  <si>
+    <t>Ta</t>
+  </si>
+  <si>
+    <t>Nb</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>Mn</t>
+  </si>
+  <si>
+    <t>Fe</t>
+  </si>
+  <si>
+    <t>Ce</t>
+  </si>
+  <si>
+    <t>Cu</t>
+  </si>
+  <si>
+    <t>Be</t>
+  </si>
+  <si>
+    <t>La</t>
+  </si>
+  <si>
+    <t>Sn</t>
   </si>
 </sst>
 </file>
@@ -824,91 +824,91 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="U1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="AD1" s="4" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/ВКР, программное обеспечение/ВКР, датасет.xlsx
+++ b/ВКР, программное обеспечение/ВКР, датасет.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\PycharmProjects\Diploma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED44AC7-2832-4DFC-B278-9CDBE1E65625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF5DB00-C1C0-44F2-A213-8E52AFDDD642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,30 +54,6 @@
   </si>
   <si>
     <t>S</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>HV10</t>
-  </si>
-  <si>
-    <t>Rm</t>
-  </si>
-  <si>
-    <t>Rp0.2</t>
-  </si>
-  <si>
-    <t>A5</t>
-  </si>
-  <si>
-    <t>КТР20-600</t>
-  </si>
-  <si>
-    <t>КТР25-500</t>
   </si>
   <si>
     <t>Ni</t>
@@ -126,6 +102,30 @@
   </si>
   <si>
     <t>Sn</t>
+  </si>
+  <si>
+    <t>g (г/см^3)</t>
+  </si>
+  <si>
+    <t>E (ГПа)</t>
+  </si>
+  <si>
+    <t>Rm (МПа)</t>
+  </si>
+  <si>
+    <t>Rp0.2 (МПа)</t>
+  </si>
+  <si>
+    <t>A5 (%)</t>
+  </si>
+  <si>
+    <t>HV10 (кгс/мм^2)</t>
+  </si>
+  <si>
+    <t>КТР20-600 (10^(-6)/K)</t>
+  </si>
+  <si>
+    <t>КТР25-500 (10^(-6)/K)</t>
   </si>
 </sst>
 </file>
@@ -816,7 +816,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="22" width="10.7109375" customWidth="1"/>
-    <col min="23" max="30" width="15.7109375" customWidth="1"/>
+    <col min="23" max="30" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -824,25 +824,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>2</v>
@@ -851,28 +851,28 @@
         <v>3</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="S1" s="3" t="s">
         <v>4</v>
@@ -881,34 +881,34 @@
         <v>5</v>
       </c>
       <c r="U1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
